--- a/resources/assets/document-templates/zh-TW/new.xlsx
+++ b/resources/assets/document-templates/zh-TW/new.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11985"/>
   </bookViews>
   <sheets>
-    <sheet name="表格1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -19,14 +19,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -54,7 +53,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常規" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
